--- a/BWI/bestwine_output/bestwine_Malta.xlsx
+++ b/BWI/bestwine_output/bestwine_Malta.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA126"/>
+  <dimension ref="A1:AA128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -13881,6 +13881,192 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>9570</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>Triq San Anton Abbati</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>MST 3102</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dicalhouse.com</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="inlineStr"/>
+      <c r="K127" s="2" t="inlineStr"/>
+      <c r="L127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr"/>
+      <c r="N127" s="2" t="inlineStr">
+        <is>
+          <t>foods@dicalgroup.com</t>
+        </is>
+      </c>
+      <c r="O127" s="2" t="inlineStr">
+        <is>
+          <t>+356 2142 4601</t>
+        </is>
+      </c>
+      <c r="P127" s="2" t="inlineStr"/>
+      <c r="Q127" s="2" t="inlineStr"/>
+      <c r="R127" s="2" t="inlineStr"/>
+      <c r="S127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DicalHouseMosta/</t>
+        </is>
+      </c>
+      <c r="T127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dicalhouse/</t>
+        </is>
+      </c>
+      <c r="U127" s="2" t="inlineStr"/>
+      <c r="V127" s="2" t="inlineStr"/>
+      <c r="W127" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Calleja</t>
+        </is>
+      </c>
+      <c r="X127" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y127" s="2" t="inlineStr"/>
+      <c r="Z127" s="2" t="inlineStr"/>
+      <c r="AA127" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dominic-calleja-57335024/?originalSubdomain=mt</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>9570</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>Triq San Anton Abbati</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>MST 3102</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dicalhouse.com</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr"/>
+      <c r="K128" s="2" t="inlineStr"/>
+      <c r="L128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr"/>
+      <c r="N128" s="2" t="inlineStr">
+        <is>
+          <t>foods@dicalgroup.com</t>
+        </is>
+      </c>
+      <c r="O128" s="2" t="inlineStr">
+        <is>
+          <t>+356 2142 4601</t>
+        </is>
+      </c>
+      <c r="P128" s="2" t="inlineStr"/>
+      <c r="Q128" s="2" t="inlineStr"/>
+      <c r="R128" s="2" t="inlineStr"/>
+      <c r="S128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DicalHouseMosta/</t>
+        </is>
+      </c>
+      <c r="T128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dicalhouse/</t>
+        </is>
+      </c>
+      <c r="U128" s="2" t="inlineStr"/>
+      <c r="V128" s="2" t="inlineStr"/>
+      <c r="W128" s="2" t="inlineStr">
+        <is>
+          <t>Anamaria Stivala</t>
+        </is>
+      </c>
+      <c r="X128" s="2" t="inlineStr">
+        <is>
+          <t>Manager And Owner</t>
+        </is>
+      </c>
+      <c r="Y128" s="2" t="inlineStr"/>
+      <c r="Z128" s="2" t="inlineStr"/>
+      <c r="AA128" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anamaria-stivala-22b26569/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Malta.xlsx
+++ b/BWI/bestwine_output/bestwine_Malta.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA128"/>
+  <dimension ref="A1:AA137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -14067,6 +14067,859 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>THE NUANCE GROUP (Malta) Limited</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>Dufry Malta</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>103888</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Luqa</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Luqa</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>Administration Building, 2nd Floor.</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>LQA 4000</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>https://malta.shopdutyfree.com</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="inlineStr"/>
+      <c r="K129" s="2" t="inlineStr"/>
+      <c r="L129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr"/>
+      <c r="N129" s="2" t="inlineStr">
+        <is>
+          <t>Tngmt@thenuancegroup.com</t>
+        </is>
+      </c>
+      <c r="O129" s="2" t="inlineStr">
+        <is>
+          <t>+356 2326 7100</t>
+        </is>
+      </c>
+      <c r="P129" s="2" t="inlineStr"/>
+      <c r="Q129" s="2" t="inlineStr"/>
+      <c r="R129" s="2" t="inlineStr"/>
+      <c r="S129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MaltaDutyFree/</t>
+        </is>
+      </c>
+      <c r="T129" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maltadutyfree/</t>
+        </is>
+      </c>
+      <c r="U129" s="2" t="inlineStr"/>
+      <c r="V129" s="2" t="inlineStr"/>
+      <c r="W129" s="2" t="inlineStr"/>
+      <c r="X129" s="2" t="inlineStr"/>
+      <c r="Y129" s="2" t="inlineStr"/>
+      <c r="Z129" s="2" t="inlineStr"/>
+      <c r="AA129" s="2" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Sa Sales Ltd</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>Sa Sales Ltd</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>9584</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>Triq l-Intornjatur, Mriehel</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>BKR 3000</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>http://sasalesltd.com</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="inlineStr"/>
+      <c r="K130" s="2" t="inlineStr"/>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr"/>
+      <c r="N130" s="2" t="inlineStr">
+        <is>
+          <t>info@sasalesltd.com</t>
+        </is>
+      </c>
+      <c r="O130" s="2" t="inlineStr">
+        <is>
+          <t>+356 2147 2449</t>
+        </is>
+      </c>
+      <c r="P130" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q130" s="2" t="inlineStr">
+        <is>
+          <t>C 55182</t>
+        </is>
+      </c>
+      <c r="R130" s="2" t="inlineStr"/>
+      <c r="S130" s="2" t="inlineStr"/>
+      <c r="T130" s="2" t="inlineStr"/>
+      <c r="U130" s="2" t="inlineStr"/>
+      <c r="V130" s="2" t="inlineStr"/>
+      <c r="W130" s="2" t="inlineStr"/>
+      <c r="X130" s="2" t="inlineStr"/>
+      <c r="Y130" s="2" t="inlineStr"/>
+      <c r="Z130" s="2" t="inlineStr"/>
+      <c r="AA130" s="2" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>9581</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>239 Tower Road</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>SLM 1601</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="inlineStr"/>
+      <c r="K131" s="2" t="inlineStr"/>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr"/>
+      <c r="N131" s="2" t="inlineStr">
+        <is>
+          <t>sales@martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="O131" s="2" t="inlineStr">
+        <is>
+          <t>+356 2097 8604</t>
+        </is>
+      </c>
+      <c r="P131" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q131" s="2" t="inlineStr">
+        <is>
+          <t>C14429</t>
+        </is>
+      </c>
+      <c r="R131" s="2" t="inlineStr"/>
+      <c r="S131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/philippe-martinet-fine-wines-174639482587570/</t>
+        </is>
+      </c>
+      <c r="T131" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/philippe_martinet_fine_wines/?hl=en</t>
+        </is>
+      </c>
+      <c r="U131" s="2" t="inlineStr"/>
+      <c r="V131" s="2" t="inlineStr"/>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet</t>
+        </is>
+      </c>
+      <c r="X131" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y131" s="2" t="inlineStr"/>
+      <c r="Z131" s="2" t="inlineStr"/>
+      <c r="AA131" s="2" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>9581</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>239 Tower Road</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>SLM 1601</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="inlineStr"/>
+      <c r="K132" s="2" t="inlineStr"/>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr"/>
+      <c r="N132" s="2" t="inlineStr">
+        <is>
+          <t>sales@martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="O132" s="2" t="inlineStr">
+        <is>
+          <t>+356 2097 8604</t>
+        </is>
+      </c>
+      <c r="P132" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q132" s="2" t="inlineStr">
+        <is>
+          <t>C14429</t>
+        </is>
+      </c>
+      <c r="R132" s="2" t="inlineStr"/>
+      <c r="S132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/philippe-martinet-fine-wines-174639482587570/</t>
+        </is>
+      </c>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/philippe_martinet_fine_wines/?hl=en</t>
+        </is>
+      </c>
+      <c r="U132" s="2" t="inlineStr"/>
+      <c r="V132" s="2" t="inlineStr"/>
+      <c r="W132" s="2" t="inlineStr">
+        <is>
+          <t>Francesca Persico</t>
+        </is>
+      </c>
+      <c r="X132" s="2" t="inlineStr">
+        <is>
+          <t>Sales Specialist</t>
+        </is>
+      </c>
+      <c r="Y132" s="2" t="inlineStr"/>
+      <c r="Z132" s="2" t="inlineStr"/>
+      <c r="AA132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/francesca-persico-949621102/</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>51840</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>182 Olaf Gollcher</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>BKR 4429</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="inlineStr"/>
+      <c r="K133" s="2" t="inlineStr"/>
+      <c r="L133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr"/>
+      <c r="N133" s="2" t="inlineStr">
+        <is>
+          <t>sales@gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="O133" s="2" t="inlineStr">
+        <is>
+          <t>+356 2033 0140</t>
+        </is>
+      </c>
+      <c r="P133" s="2" t="inlineStr"/>
+      <c r="Q133" s="2" t="inlineStr"/>
+      <c r="R133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gift-hampers/</t>
+        </is>
+      </c>
+      <c r="S133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GiftHampersIntl</t>
+        </is>
+      </c>
+      <c r="T133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gifthampersintl/</t>
+        </is>
+      </c>
+      <c r="U133" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/gifthampersintl</t>
+        </is>
+      </c>
+      <c r="V133" s="2" t="inlineStr"/>
+      <c r="W133" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Booth</t>
+        </is>
+      </c>
+      <c r="X133" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y133" s="2" t="inlineStr"/>
+      <c r="Z133" s="2" t="inlineStr"/>
+      <c r="AA133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarahcarterbooth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>51840</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>182 Olaf Gollcher</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>BKR 4429</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="inlineStr"/>
+      <c r="K134" s="2" t="inlineStr"/>
+      <c r="L134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr"/>
+      <c r="N134" s="2" t="inlineStr">
+        <is>
+          <t>sales@gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="O134" s="2" t="inlineStr">
+        <is>
+          <t>+356 2033 0140</t>
+        </is>
+      </c>
+      <c r="P134" s="2" t="inlineStr"/>
+      <c r="Q134" s="2" t="inlineStr"/>
+      <c r="R134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gift-hampers/</t>
+        </is>
+      </c>
+      <c r="S134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GiftHampersIntl</t>
+        </is>
+      </c>
+      <c r="T134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gifthampersintl/</t>
+        </is>
+      </c>
+      <c r="U134" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/gifthampersintl</t>
+        </is>
+      </c>
+      <c r="V134" s="2" t="inlineStr"/>
+      <c r="W134" s="2" t="inlineStr">
+        <is>
+          <t>Jon Fava</t>
+        </is>
+      </c>
+      <c r="X134" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y134" s="2" t="inlineStr"/>
+      <c r="Z134" s="2" t="inlineStr"/>
+      <c r="AA134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jonfava/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Cellars Ltd.</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Cellars Ltd.</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>9580</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Birżebbuġa</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>164, Birżebbġa Road</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>BBG1507</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.patrickcellars.com</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="inlineStr"/>
+      <c r="K135" s="2" t="inlineStr"/>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr"/>
+      <c r="N135" s="2" t="inlineStr">
+        <is>
+          <t>info@patrickcellars.com</t>
+        </is>
+      </c>
+      <c r="O135" s="2" t="inlineStr">
+        <is>
+          <t>+356 2165 0810</t>
+        </is>
+      </c>
+      <c r="P135" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q135" s="2" t="inlineStr">
+        <is>
+          <t>C 15930</t>
+        </is>
+      </c>
+      <c r="R135" s="2" t="inlineStr"/>
+      <c r="S135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PatrickCellarsltd</t>
+        </is>
+      </c>
+      <c r="T135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/patrick_cellars_ltd/</t>
+        </is>
+      </c>
+      <c r="U135" s="2" t="inlineStr"/>
+      <c r="V135" s="2" t="inlineStr"/>
+      <c r="W135" s="2" t="inlineStr"/>
+      <c r="X135" s="2" t="inlineStr"/>
+      <c r="Y135" s="2" t="inlineStr"/>
+      <c r="Z135" s="2" t="inlineStr"/>
+      <c r="AA135" s="2" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>9570</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>Triq San Anton Abbati</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>MST 3102</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dicalhouse.com</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="inlineStr"/>
+      <c r="K136" s="2" t="inlineStr"/>
+      <c r="L136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr"/>
+      <c r="N136" s="2" t="inlineStr">
+        <is>
+          <t>foods@dicalgroup.com</t>
+        </is>
+      </c>
+      <c r="O136" s="2" t="inlineStr">
+        <is>
+          <t>+356 2142 4601</t>
+        </is>
+      </c>
+      <c r="P136" s="2" t="inlineStr"/>
+      <c r="Q136" s="2" t="inlineStr"/>
+      <c r="R136" s="2" t="inlineStr"/>
+      <c r="S136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DicalHouseMosta/</t>
+        </is>
+      </c>
+      <c r="T136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dicalhouse/</t>
+        </is>
+      </c>
+      <c r="U136" s="2" t="inlineStr"/>
+      <c r="V136" s="2" t="inlineStr"/>
+      <c r="W136" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Calleja</t>
+        </is>
+      </c>
+      <c r="X136" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y136" s="2" t="inlineStr"/>
+      <c r="Z136" s="2" t="inlineStr"/>
+      <c r="AA136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dominic-calleja-57335024/?originalSubdomain=mt</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>9570</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>Triq San Anton Abbati</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>MST 3102</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dicalhouse.com</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr"/>
+      <c r="K137" s="2" t="inlineStr"/>
+      <c r="L137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr"/>
+      <c r="N137" s="2" t="inlineStr">
+        <is>
+          <t>foods@dicalgroup.com</t>
+        </is>
+      </c>
+      <c r="O137" s="2" t="inlineStr">
+        <is>
+          <t>+356 2142 4601</t>
+        </is>
+      </c>
+      <c r="P137" s="2" t="inlineStr"/>
+      <c r="Q137" s="2" t="inlineStr"/>
+      <c r="R137" s="2" t="inlineStr"/>
+      <c r="S137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DicalHouseMosta/</t>
+        </is>
+      </c>
+      <c r="T137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dicalhouse/</t>
+        </is>
+      </c>
+      <c r="U137" s="2" t="inlineStr"/>
+      <c r="V137" s="2" t="inlineStr"/>
+      <c r="W137" s="2" t="inlineStr">
+        <is>
+          <t>Anamaria Stivala</t>
+        </is>
+      </c>
+      <c r="X137" s="2" t="inlineStr">
+        <is>
+          <t>Manager And Owner</t>
+        </is>
+      </c>
+      <c r="Y137" s="2" t="inlineStr"/>
+      <c r="Z137" s="2" t="inlineStr"/>
+      <c r="AA137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anamaria-stivala-22b26569/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Malta.xlsx
+++ b/BWI/bestwine_output/bestwine_Malta.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA137"/>
+  <dimension ref="A1:AA152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -14920,6 +14920,1409 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>The Master Cellar</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>The Master Cellar</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>21663</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>In-Naxxar</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>In-Naxxar</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>40 Triq l-Oratorju</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.themastercellar.com</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>info@themastercellar.com</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr">
+        <is>
+          <t>+356 2141 7666</t>
+        </is>
+      </c>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr"/>
+      <c r="R138" s="2" t="inlineStr"/>
+      <c r="S138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/themastercellar/</t>
+        </is>
+      </c>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/themastercellar_mt/</t>
+        </is>
+      </c>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr"/>
+      <c r="X138" s="2" t="inlineStr"/>
+      <c r="Y138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Iv Cellars Malta</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Iv Cellars Malta</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>9574</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>Sir Arturo Mercieca Street (adjacent To The Diplomat Hotel)</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>SLM 1861</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ivcellarsmalta.com</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>info@ivcellarsmalta.com</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr">
+        <is>
+          <t>+356 2746 0534</t>
+        </is>
+      </c>
+      <c r="P139" s="2" t="inlineStr"/>
+      <c r="Q139" s="2" t="inlineStr"/>
+      <c r="R139" s="2" t="inlineStr"/>
+      <c r="S139" s="2" t="inlineStr"/>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iv_cellars_malta/</t>
+        </is>
+      </c>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr"/>
+      <c r="X139" s="2" t="inlineStr"/>
+      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Cleland &amp; Souchet Ltd.</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Cleland &amp; Souchet Ltd.</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>9569</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>San Ġiljan</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>San Ġiljan</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Block 14, Portomaso</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>STJ 4013</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clelandsouchet.com</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>retail@clelandsouchet.com</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr">
+        <is>
+          <t>+356 2138 9898</t>
+        </is>
+      </c>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>C 24996</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr"/>
+      <c r="S140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/clelandsouchet/</t>
+        </is>
+      </c>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cleland_souchet</t>
+        </is>
+      </c>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr">
+        <is>
+          <t>Richard Cleland</t>
+        </is>
+      </c>
+      <c r="X140" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-cleland-7439648/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Holy Wines</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Holy Wines</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>51439</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Mosta</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Mosta</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>Saint Anne Street</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>MGR 2113</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.holywines.com.mt</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="inlineStr"/>
+      <c r="K141" s="2" t="inlineStr"/>
+      <c r="L141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr"/>
+      <c r="N141" s="2" t="inlineStr">
+        <is>
+          <t>adrian@holywines.com.mt</t>
+        </is>
+      </c>
+      <c r="O141" s="2" t="inlineStr"/>
+      <c r="P141" s="2" t="inlineStr"/>
+      <c r="Q141" s="2" t="inlineStr"/>
+      <c r="R141" s="2" t="inlineStr"/>
+      <c r="S141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/holywines.com.mt/</t>
+        </is>
+      </c>
+      <c r="T141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/holy.wines/</t>
+        </is>
+      </c>
+      <c r="U141" s="2" t="inlineStr"/>
+      <c r="V141" s="2" t="inlineStr"/>
+      <c r="W141" s="2" t="inlineStr">
+        <is>
+          <t>Adrian Mizzi</t>
+        </is>
+      </c>
+      <c r="X141" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y141" s="2" t="inlineStr"/>
+      <c r="Z141" s="2" t="inlineStr"/>
+      <c r="AA141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adrian-mizzi-881a48254/</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Simonds Farsons Cisk Plc</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Simonds Farsons Cisk Plc</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>9587</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Mriehel</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Mriehel</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>The Brewery, Mdina Road</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>CBD 2010</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.farsons.com</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="inlineStr"/>
+      <c r="K142" s="2" t="inlineStr"/>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr"/>
+      <c r="N142" s="2" t="inlineStr">
+        <is>
+          <t>careers@farsons.com</t>
+        </is>
+      </c>
+      <c r="O142" s="2" t="inlineStr">
+        <is>
+          <t>+356 2381 4114</t>
+        </is>
+      </c>
+      <c r="P142" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="Q142" s="2" t="inlineStr">
+        <is>
+          <t>C 113</t>
+        </is>
+      </c>
+      <c r="R142" s="2" t="inlineStr"/>
+      <c r="S142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/farsonsgroup/</t>
+        </is>
+      </c>
+      <c r="T142" s="2" t="inlineStr"/>
+      <c r="U142" s="2" t="inlineStr"/>
+      <c r="V142" s="2" t="inlineStr"/>
+      <c r="W142" s="2" t="inlineStr"/>
+      <c r="X142" s="2" t="inlineStr"/>
+      <c r="Y142" s="2" t="inlineStr"/>
+      <c r="Z142" s="2" t="inlineStr"/>
+      <c r="AA142" s="2" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Farsons Beverage Imports Company Limited</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Farsons Beverage Imports Company Limited</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>9593</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Mdina</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Mdina</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>The Brewery, Mdina Road, Zone 2, Central Business District</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>cbd2010</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>https://farsonsdirect.com</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr"/>
+      <c r="K143" s="2" t="inlineStr"/>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr"/>
+      <c r="N143" s="2" t="inlineStr">
+        <is>
+          <t>info@farsonsdirect.com</t>
+        </is>
+      </c>
+      <c r="O143" s="2" t="inlineStr">
+        <is>
+          <t>+356 2381 4444</t>
+        </is>
+      </c>
+      <c r="P143" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="Q143" s="2" t="inlineStr">
+        <is>
+          <t>C 476</t>
+        </is>
+      </c>
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farsonsdirect/</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/farsonsdirect/</t>
+        </is>
+      </c>
+      <c r="T143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/farsonsdirect/</t>
+        </is>
+      </c>
+      <c r="U143" s="2" t="inlineStr"/>
+      <c r="V143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@farsonsdirect1770</t>
+        </is>
+      </c>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
+          <t>Petar Mladenovic</t>
+        </is>
+      </c>
+      <c r="X143" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y143" s="2" t="inlineStr"/>
+      <c r="Z143" s="2" t="inlineStr"/>
+      <c r="AA143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/petar-mladenovic-1a9745145/</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>THE NUANCE GROUP (Malta) Limited</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Dufry Malta</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>103888</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Luqa</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Luqa</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>Administration Building, 2nd Floor.</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>LQA 4000</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>https://malta.shopdutyfree.com</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="inlineStr"/>
+      <c r="K144" s="2" t="inlineStr"/>
+      <c r="L144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr"/>
+      <c r="N144" s="2" t="inlineStr">
+        <is>
+          <t>Tngmt@thenuancegroup.com</t>
+        </is>
+      </c>
+      <c r="O144" s="2" t="inlineStr">
+        <is>
+          <t>+356 2326 7100</t>
+        </is>
+      </c>
+      <c r="P144" s="2" t="inlineStr"/>
+      <c r="Q144" s="2" t="inlineStr"/>
+      <c r="R144" s="2" t="inlineStr"/>
+      <c r="S144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MaltaDutyFree/</t>
+        </is>
+      </c>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maltadutyfree/</t>
+        </is>
+      </c>
+      <c r="U144" s="2" t="inlineStr"/>
+      <c r="V144" s="2" t="inlineStr"/>
+      <c r="W144" s="2" t="inlineStr"/>
+      <c r="X144" s="2" t="inlineStr"/>
+      <c r="Y144" s="2" t="inlineStr"/>
+      <c r="Z144" s="2" t="inlineStr"/>
+      <c r="AA144" s="2" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Sa Sales Ltd</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Sa Sales Ltd</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>9584</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>Triq l-Intornjatur, Mriehel</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>BKR 3000</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>http://sasalesltd.com</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="inlineStr"/>
+      <c r="K145" s="2" t="inlineStr"/>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr"/>
+      <c r="N145" s="2" t="inlineStr">
+        <is>
+          <t>info@sasalesltd.com</t>
+        </is>
+      </c>
+      <c r="O145" s="2" t="inlineStr">
+        <is>
+          <t>+356 2147 2449</t>
+        </is>
+      </c>
+      <c r="P145" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q145" s="2" t="inlineStr">
+        <is>
+          <t>C 55182</t>
+        </is>
+      </c>
+      <c r="R145" s="2" t="inlineStr"/>
+      <c r="S145" s="2" t="inlineStr"/>
+      <c r="T145" s="2" t="inlineStr"/>
+      <c r="U145" s="2" t="inlineStr"/>
+      <c r="V145" s="2" t="inlineStr"/>
+      <c r="W145" s="2" t="inlineStr"/>
+      <c r="X145" s="2" t="inlineStr"/>
+      <c r="Y145" s="2" t="inlineStr"/>
+      <c r="Z145" s="2" t="inlineStr"/>
+      <c r="AA145" s="2" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>9581</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>239 Tower Road</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>SLM 1601</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="inlineStr"/>
+      <c r="K146" s="2" t="inlineStr"/>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr"/>
+      <c r="N146" s="2" t="inlineStr">
+        <is>
+          <t>sales@martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="O146" s="2" t="inlineStr">
+        <is>
+          <t>+356 2097 8604</t>
+        </is>
+      </c>
+      <c r="P146" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q146" s="2" t="inlineStr">
+        <is>
+          <t>C14429</t>
+        </is>
+      </c>
+      <c r="R146" s="2" t="inlineStr"/>
+      <c r="S146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/philippe-martinet-fine-wines-174639482587570/</t>
+        </is>
+      </c>
+      <c r="T146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/philippe_martinet_fine_wines/?hl=en</t>
+        </is>
+      </c>
+      <c r="U146" s="2" t="inlineStr"/>
+      <c r="V146" s="2" t="inlineStr"/>
+      <c r="W146" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet</t>
+        </is>
+      </c>
+      <c r="X146" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y146" s="2" t="inlineStr"/>
+      <c r="Z146" s="2" t="inlineStr"/>
+      <c r="AA146" s="2" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>9581</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>239 Tower Road</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>SLM 1601</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="inlineStr"/>
+      <c r="K147" s="2" t="inlineStr"/>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr"/>
+      <c r="N147" s="2" t="inlineStr">
+        <is>
+          <t>sales@martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="O147" s="2" t="inlineStr">
+        <is>
+          <t>+356 2097 8604</t>
+        </is>
+      </c>
+      <c r="P147" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q147" s="2" t="inlineStr">
+        <is>
+          <t>C14429</t>
+        </is>
+      </c>
+      <c r="R147" s="2" t="inlineStr"/>
+      <c r="S147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/philippe-martinet-fine-wines-174639482587570/</t>
+        </is>
+      </c>
+      <c r="T147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/philippe_martinet_fine_wines/?hl=en</t>
+        </is>
+      </c>
+      <c r="U147" s="2" t="inlineStr"/>
+      <c r="V147" s="2" t="inlineStr"/>
+      <c r="W147" s="2" t="inlineStr">
+        <is>
+          <t>Francesca Persico</t>
+        </is>
+      </c>
+      <c r="X147" s="2" t="inlineStr">
+        <is>
+          <t>Sales Specialist</t>
+        </is>
+      </c>
+      <c r="Y147" s="2" t="inlineStr"/>
+      <c r="Z147" s="2" t="inlineStr"/>
+      <c r="AA147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/francesca-persico-949621102/</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>51840</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>182 Olaf Gollcher</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>BKR 4429</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="inlineStr"/>
+      <c r="K148" s="2" t="inlineStr"/>
+      <c r="L148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr"/>
+      <c r="N148" s="2" t="inlineStr">
+        <is>
+          <t>sales@gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="O148" s="2" t="inlineStr">
+        <is>
+          <t>+356 2033 0140</t>
+        </is>
+      </c>
+      <c r="P148" s="2" t="inlineStr"/>
+      <c r="Q148" s="2" t="inlineStr"/>
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gift-hampers/</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GiftHampersIntl</t>
+        </is>
+      </c>
+      <c r="T148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gifthampersintl/</t>
+        </is>
+      </c>
+      <c r="U148" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/gifthampersintl</t>
+        </is>
+      </c>
+      <c r="V148" s="2" t="inlineStr"/>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Booth</t>
+        </is>
+      </c>
+      <c r="X148" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y148" s="2" t="inlineStr"/>
+      <c r="Z148" s="2" t="inlineStr"/>
+      <c r="AA148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarahcarterbooth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>51840</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr">
+        <is>
+          <t>182 Olaf Gollcher</t>
+        </is>
+      </c>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t>BKR 4429</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr"/>
+      <c r="K149" s="2" t="inlineStr"/>
+      <c r="L149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr"/>
+      <c r="N149" s="2" t="inlineStr">
+        <is>
+          <t>sales@gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="O149" s="2" t="inlineStr">
+        <is>
+          <t>+356 2033 0140</t>
+        </is>
+      </c>
+      <c r="P149" s="2" t="inlineStr"/>
+      <c r="Q149" s="2" t="inlineStr"/>
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gift-hampers/</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GiftHampersIntl</t>
+        </is>
+      </c>
+      <c r="T149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gifthampersintl/</t>
+        </is>
+      </c>
+      <c r="U149" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/gifthampersintl</t>
+        </is>
+      </c>
+      <c r="V149" s="2" t="inlineStr"/>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
+          <t>Jon Fava</t>
+        </is>
+      </c>
+      <c r="X149" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y149" s="2" t="inlineStr"/>
+      <c r="Z149" s="2" t="inlineStr"/>
+      <c r="AA149" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jonfava/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Cellars Ltd.</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Cellars Ltd.</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>9580</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E150" s="2" t="inlineStr">
+        <is>
+          <t>Birżebbuġa</t>
+        </is>
+      </c>
+      <c r="F150" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>164, Birżebbġa Road</t>
+        </is>
+      </c>
+      <c r="H150" s="2" t="inlineStr">
+        <is>
+          <t>BBG1507</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.patrickcellars.com</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="inlineStr"/>
+      <c r="K150" s="2" t="inlineStr"/>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr"/>
+      <c r="N150" s="2" t="inlineStr">
+        <is>
+          <t>info@patrickcellars.com</t>
+        </is>
+      </c>
+      <c r="O150" s="2" t="inlineStr">
+        <is>
+          <t>+356 2165 0810</t>
+        </is>
+      </c>
+      <c r="P150" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q150" s="2" t="inlineStr">
+        <is>
+          <t>C 15930</t>
+        </is>
+      </c>
+      <c r="R150" s="2" t="inlineStr"/>
+      <c r="S150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PatrickCellarsltd</t>
+        </is>
+      </c>
+      <c r="T150" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/patrick_cellars_ltd/</t>
+        </is>
+      </c>
+      <c r="U150" s="2" t="inlineStr"/>
+      <c r="V150" s="2" t="inlineStr"/>
+      <c r="W150" s="2" t="inlineStr"/>
+      <c r="X150" s="2" t="inlineStr"/>
+      <c r="Y150" s="2" t="inlineStr"/>
+      <c r="Z150" s="2" t="inlineStr"/>
+      <c r="AA150" s="2" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>9570</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="F151" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="G151" s="2" t="inlineStr">
+        <is>
+          <t>Triq San Anton Abbati</t>
+        </is>
+      </c>
+      <c r="H151" s="2" t="inlineStr">
+        <is>
+          <t>MST 3102</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dicalhouse.com</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="inlineStr"/>
+      <c r="K151" s="2" t="inlineStr"/>
+      <c r="L151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="inlineStr"/>
+      <c r="N151" s="2" t="inlineStr">
+        <is>
+          <t>foods@dicalgroup.com</t>
+        </is>
+      </c>
+      <c r="O151" s="2" t="inlineStr">
+        <is>
+          <t>+356 2142 4601</t>
+        </is>
+      </c>
+      <c r="P151" s="2" t="inlineStr"/>
+      <c r="Q151" s="2" t="inlineStr"/>
+      <c r="R151" s="2" t="inlineStr"/>
+      <c r="S151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DicalHouseMosta/</t>
+        </is>
+      </c>
+      <c r="T151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dicalhouse/</t>
+        </is>
+      </c>
+      <c r="U151" s="2" t="inlineStr"/>
+      <c r="V151" s="2" t="inlineStr"/>
+      <c r="W151" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Calleja</t>
+        </is>
+      </c>
+      <c r="X151" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y151" s="2" t="inlineStr"/>
+      <c r="Z151" s="2" t="inlineStr"/>
+      <c r="AA151" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dominic-calleja-57335024/?originalSubdomain=mt</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>9570</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="F152" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="G152" s="2" t="inlineStr">
+        <is>
+          <t>Triq San Anton Abbati</t>
+        </is>
+      </c>
+      <c r="H152" s="2" t="inlineStr">
+        <is>
+          <t>MST 3102</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dicalhouse.com</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="inlineStr"/>
+      <c r="K152" s="2" t="inlineStr"/>
+      <c r="L152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr"/>
+      <c r="N152" s="2" t="inlineStr">
+        <is>
+          <t>foods@dicalgroup.com</t>
+        </is>
+      </c>
+      <c r="O152" s="2" t="inlineStr">
+        <is>
+          <t>+356 2142 4601</t>
+        </is>
+      </c>
+      <c r="P152" s="2" t="inlineStr"/>
+      <c r="Q152" s="2" t="inlineStr"/>
+      <c r="R152" s="2" t="inlineStr"/>
+      <c r="S152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DicalHouseMosta/</t>
+        </is>
+      </c>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dicalhouse/</t>
+        </is>
+      </c>
+      <c r="U152" s="2" t="inlineStr"/>
+      <c r="V152" s="2" t="inlineStr"/>
+      <c r="W152" s="2" t="inlineStr">
+        <is>
+          <t>Anamaria Stivala</t>
+        </is>
+      </c>
+      <c r="X152" s="2" t="inlineStr">
+        <is>
+          <t>Manager And Owner</t>
+        </is>
+      </c>
+      <c r="Y152" s="2" t="inlineStr"/>
+      <c r="Z152" s="2" t="inlineStr"/>
+      <c r="AA152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anamaria-stivala-22b26569/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Malta.xlsx
+++ b/BWI/bestwine_output/bestwine_Malta.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA152"/>
+  <dimension ref="A1:AA172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -16323,6 +16323,1902 @@
         </is>
       </c>
     </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>Casa Vini</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>Casa Vini</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>21449</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E153" s="2" t="inlineStr">
+        <is>
+          <t>Fgura</t>
+        </is>
+      </c>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="G153" s="2" t="inlineStr">
+        <is>
+          <t>325/327, Triq Zabbar</t>
+        </is>
+      </c>
+      <c r="H153" s="2" t="inlineStr"/>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>https://casavini.com.mt</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="inlineStr"/>
+      <c r="K153" s="2" t="inlineStr"/>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr"/>
+      <c r="N153" s="2" t="inlineStr">
+        <is>
+          <t>sales@casavini.com.mt</t>
+        </is>
+      </c>
+      <c r="O153" s="2" t="inlineStr"/>
+      <c r="P153" s="2" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="Q153" s="2" t="inlineStr">
+        <is>
+          <t>C 41106</t>
+        </is>
+      </c>
+      <c r="R153" s="2" t="inlineStr"/>
+      <c r="S153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/casaviniwines/</t>
+        </is>
+      </c>
+      <c r="T153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/casavini_gozo.distributor/</t>
+        </is>
+      </c>
+      <c r="U153" s="2" t="inlineStr"/>
+      <c r="V153" s="2" t="inlineStr"/>
+      <c r="W153" s="2" t="inlineStr">
+        <is>
+          <t>Max Castagna</t>
+        </is>
+      </c>
+      <c r="X153" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y153" s="2" t="inlineStr"/>
+      <c r="Z153" s="2" t="inlineStr"/>
+      <c r="AA153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/max-castagna-91b48242/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>Fava Trading Limited</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>Fava Trading Limited</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>40046</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E154" s="2" t="inlineStr">
+        <is>
+          <t>Qormi</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Qormi</t>
+        </is>
+      </c>
+      <c r="G154" s="2" t="inlineStr">
+        <is>
+          <t>Triq Mro. Giuseppe Camilleri, Tal Handaq</t>
+        </is>
+      </c>
+      <c r="H154" s="2" t="inlineStr">
+        <is>
+          <t>QRM4000</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.favatrading.com</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr"/>
+      <c r="K154" s="2" t="inlineStr"/>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr"/>
+      <c r="N154" s="2" t="inlineStr">
+        <is>
+          <t>info@favatrading.com</t>
+        </is>
+      </c>
+      <c r="O154" s="2" t="inlineStr">
+        <is>
+          <t>+356 2137 6929</t>
+        </is>
+      </c>
+      <c r="P154" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q154" s="2" t="inlineStr">
+        <is>
+          <t>C 21368</t>
+        </is>
+      </c>
+      <c r="R154" s="2" t="inlineStr"/>
+      <c r="S154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/favatradingltd/</t>
+        </is>
+      </c>
+      <c r="T154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/favatradingmalta</t>
+        </is>
+      </c>
+      <c r="U154" s="2" t="inlineStr"/>
+      <c r="V154" s="2" t="inlineStr"/>
+      <c r="W154" s="2" t="inlineStr">
+        <is>
+          <t>Sandra Fava</t>
+        </is>
+      </c>
+      <c r="X154" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y154" s="2" t="inlineStr"/>
+      <c r="Z154" s="2" t="inlineStr"/>
+      <c r="AA154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sandra-fava-21054337/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>Fava Trading Limited</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>Fava Trading Limited</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>40046</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>Qormi</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="inlineStr">
+        <is>
+          <t>Qormi</t>
+        </is>
+      </c>
+      <c r="G155" s="2" t="inlineStr">
+        <is>
+          <t>Triq Mro. Giuseppe Camilleri, Tal Handaq</t>
+        </is>
+      </c>
+      <c r="H155" s="2" t="inlineStr">
+        <is>
+          <t>QRM4000</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.favatrading.com</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="inlineStr"/>
+      <c r="K155" s="2" t="inlineStr"/>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr"/>
+      <c r="N155" s="2" t="inlineStr">
+        <is>
+          <t>info@favatrading.com</t>
+        </is>
+      </c>
+      <c r="O155" s="2" t="inlineStr">
+        <is>
+          <t>+356 2137 6929</t>
+        </is>
+      </c>
+      <c r="P155" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>C 21368</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr"/>
+      <c r="S155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/favatradingltd/</t>
+        </is>
+      </c>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/favatradingmalta</t>
+        </is>
+      </c>
+      <c r="U155" s="2" t="inlineStr"/>
+      <c r="V155" s="2" t="inlineStr"/>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>Mario Fava</t>
+        </is>
+      </c>
+      <c r="X155" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y155" s="2" t="inlineStr"/>
+      <c r="Z155" s="2" t="inlineStr"/>
+      <c r="AA155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/mario-fava-79787111a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Nm Arrigo Limited</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Nm Arrigo Limited</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>9578</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="F156" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="G156" s="2" t="inlineStr">
+        <is>
+          <t>Triq L-Intornjatur</t>
+        </is>
+      </c>
+      <c r="H156" s="2" t="inlineStr">
+        <is>
+          <t>BKR 3000</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.nmarrigo.com</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="inlineStr"/>
+      <c r="K156" s="2" t="inlineStr"/>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr"/>
+      <c r="N156" s="2" t="inlineStr">
+        <is>
+          <t>info@nmarrigo.com</t>
+        </is>
+      </c>
+      <c r="O156" s="2" t="inlineStr">
+        <is>
+          <t>+356 2122 5039</t>
+        </is>
+      </c>
+      <c r="P156" s="2" t="inlineStr">
+        <is>
+          <t>1983</t>
+        </is>
+      </c>
+      <c r="Q156" s="2" t="inlineStr">
+        <is>
+          <t>C 6283</t>
+        </is>
+      </c>
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/nm-arrigo-ltd</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="inlineStr"/>
+      <c r="T156" s="2" t="inlineStr"/>
+      <c r="U156" s="2" t="inlineStr"/>
+      <c r="V156" s="2" t="inlineStr"/>
+      <c r="W156" s="2" t="inlineStr">
+        <is>
+          <t>Svetlin Mladenov</t>
+        </is>
+      </c>
+      <c r="X156" s="2" t="inlineStr">
+        <is>
+          <t>Retail Manager</t>
+        </is>
+      </c>
+      <c r="Y156" s="2" t="inlineStr"/>
+      <c r="Z156" s="2" t="inlineStr"/>
+      <c r="AA156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/svetlin-mladenov-156600105/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>Island Beverages Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>Island Beverages Co. Ltd.</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>55905</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E157" s="2" t="inlineStr">
+        <is>
+          <t>Attard</t>
+        </is>
+      </c>
+      <c r="F157" s="2" t="inlineStr">
+        <is>
+          <t>Attard</t>
+        </is>
+      </c>
+      <c r="G157" s="2" t="inlineStr">
+        <is>
+          <t>Atp 06, Industrial Estate</t>
+        </is>
+      </c>
+      <c r="H157" s="2" t="inlineStr">
+        <is>
+          <t>ATD 3000</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>https://islandbeverages.com</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="inlineStr"/>
+      <c r="K157" s="2" t="inlineStr"/>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr"/>
+      <c r="N157" s="2" t="inlineStr">
+        <is>
+          <t>sales@islandbeverages.com</t>
+        </is>
+      </c>
+      <c r="O157" s="2" t="inlineStr">
+        <is>
+          <t>+356 2142 0420</t>
+        </is>
+      </c>
+      <c r="P157" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q157" s="2" t="inlineStr">
+        <is>
+          <t>C 17349</t>
+        </is>
+      </c>
+      <c r="R157" s="2" t="inlineStr"/>
+      <c r="S157" s="2" t="inlineStr"/>
+      <c r="T157" s="2" t="inlineStr"/>
+      <c r="U157" s="2" t="inlineStr"/>
+      <c r="V157" s="2" t="inlineStr"/>
+      <c r="W157" s="2" t="inlineStr"/>
+      <c r="X157" s="2" t="inlineStr"/>
+      <c r="Y157" s="2" t="inlineStr"/>
+      <c r="Z157" s="2" t="inlineStr"/>
+      <c r="AA157" s="2" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>The Master Cellar</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>The Master Cellar</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>21663</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="inlineStr">
+        <is>
+          <t>In-Naxxar</t>
+        </is>
+      </c>
+      <c r="F158" s="2" t="inlineStr">
+        <is>
+          <t>In-Naxxar</t>
+        </is>
+      </c>
+      <c r="G158" s="2" t="inlineStr">
+        <is>
+          <t>40 Triq l-Oratorju</t>
+        </is>
+      </c>
+      <c r="H158" s="2" t="inlineStr"/>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.themastercellar.com</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="inlineStr"/>
+      <c r="K158" s="2" t="inlineStr"/>
+      <c r="L158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr"/>
+      <c r="N158" s="2" t="inlineStr">
+        <is>
+          <t>info@themastercellar.com</t>
+        </is>
+      </c>
+      <c r="O158" s="2" t="inlineStr">
+        <is>
+          <t>+356 2141 7666</t>
+        </is>
+      </c>
+      <c r="P158" s="2" t="inlineStr"/>
+      <c r="Q158" s="2" t="inlineStr"/>
+      <c r="R158" s="2" t="inlineStr"/>
+      <c r="S158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/themastercellar/</t>
+        </is>
+      </c>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/themastercellar_mt/</t>
+        </is>
+      </c>
+      <c r="U158" s="2" t="inlineStr"/>
+      <c r="V158" s="2" t="inlineStr"/>
+      <c r="W158" s="2" t="inlineStr"/>
+      <c r="X158" s="2" t="inlineStr"/>
+      <c r="Y158" s="2" t="inlineStr"/>
+      <c r="Z158" s="2" t="inlineStr"/>
+      <c r="AA158" s="2" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>Iv Cellars Malta</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>Iv Cellars Malta</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>9574</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="F159" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="G159" s="2" t="inlineStr">
+        <is>
+          <t>Sir Arturo Mercieca Street (adjacent To The Diplomat Hotel)</t>
+        </is>
+      </c>
+      <c r="H159" s="2" t="inlineStr">
+        <is>
+          <t>SLM 1861</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.ivcellarsmalta.com</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="inlineStr"/>
+      <c r="K159" s="2" t="inlineStr"/>
+      <c r="L159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr"/>
+      <c r="N159" s="2" t="inlineStr">
+        <is>
+          <t>info@ivcellarsmalta.com</t>
+        </is>
+      </c>
+      <c r="O159" s="2" t="inlineStr">
+        <is>
+          <t>+356 2746 0534</t>
+        </is>
+      </c>
+      <c r="P159" s="2" t="inlineStr"/>
+      <c r="Q159" s="2" t="inlineStr"/>
+      <c r="R159" s="2" t="inlineStr"/>
+      <c r="S159" s="2" t="inlineStr"/>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/iv_cellars_malta/</t>
+        </is>
+      </c>
+      <c r="U159" s="2" t="inlineStr"/>
+      <c r="V159" s="2" t="inlineStr"/>
+      <c r="W159" s="2" t="inlineStr"/>
+      <c r="X159" s="2" t="inlineStr"/>
+      <c r="Y159" s="2" t="inlineStr"/>
+      <c r="Z159" s="2" t="inlineStr"/>
+      <c r="AA159" s="2" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>Cleland &amp; Souchet Ltd.</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>Cleland &amp; Souchet Ltd.</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>9569</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E160" s="2" t="inlineStr">
+        <is>
+          <t>San Ġiljan</t>
+        </is>
+      </c>
+      <c r="F160" s="2" t="inlineStr">
+        <is>
+          <t>San Ġiljan</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>Block 14, Portomaso</t>
+        </is>
+      </c>
+      <c r="H160" s="2" t="inlineStr">
+        <is>
+          <t>STJ 4013</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.clelandsouchet.com</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr"/>
+      <c r="K160" s="2" t="inlineStr"/>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr"/>
+      <c r="N160" s="2" t="inlineStr">
+        <is>
+          <t>retail@clelandsouchet.com</t>
+        </is>
+      </c>
+      <c r="O160" s="2" t="inlineStr">
+        <is>
+          <t>+356 2138 9898</t>
+        </is>
+      </c>
+      <c r="P160" s="2" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="Q160" s="2" t="inlineStr">
+        <is>
+          <t>C 24996</t>
+        </is>
+      </c>
+      <c r="R160" s="2" t="inlineStr"/>
+      <c r="S160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/clelandsouchet/</t>
+        </is>
+      </c>
+      <c r="T160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cleland_souchet</t>
+        </is>
+      </c>
+      <c r="U160" s="2" t="inlineStr"/>
+      <c r="V160" s="2" t="inlineStr"/>
+      <c r="W160" s="2" t="inlineStr">
+        <is>
+          <t>Richard Cleland</t>
+        </is>
+      </c>
+      <c r="X160" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y160" s="2" t="inlineStr"/>
+      <c r="Z160" s="2" t="inlineStr"/>
+      <c r="AA160" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/richard-cleland-7439648/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>Holy Wines</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>Holy Wines</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>51439</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="inlineStr">
+        <is>
+          <t>Mosta</t>
+        </is>
+      </c>
+      <c r="F161" s="2" t="inlineStr">
+        <is>
+          <t>Mosta</t>
+        </is>
+      </c>
+      <c r="G161" s="2" t="inlineStr">
+        <is>
+          <t>Saint Anne Street</t>
+        </is>
+      </c>
+      <c r="H161" s="2" t="inlineStr">
+        <is>
+          <t>MGR 2113</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.holywines.com.mt</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="inlineStr"/>
+      <c r="K161" s="2" t="inlineStr"/>
+      <c r="L161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr"/>
+      <c r="N161" s="2" t="inlineStr">
+        <is>
+          <t>adrian@holywines.com.mt</t>
+        </is>
+      </c>
+      <c r="O161" s="2" t="inlineStr"/>
+      <c r="P161" s="2" t="inlineStr"/>
+      <c r="Q161" s="2" t="inlineStr"/>
+      <c r="R161" s="2" t="inlineStr"/>
+      <c r="S161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/holywines.com.mt/</t>
+        </is>
+      </c>
+      <c r="T161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/holy.wines/</t>
+        </is>
+      </c>
+      <c r="U161" s="2" t="inlineStr"/>
+      <c r="V161" s="2" t="inlineStr"/>
+      <c r="W161" s="2" t="inlineStr">
+        <is>
+          <t>Adrian Mizzi</t>
+        </is>
+      </c>
+      <c r="X161" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y161" s="2" t="inlineStr"/>
+      <c r="Z161" s="2" t="inlineStr"/>
+      <c r="AA161" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adrian-mizzi-881a48254/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>Simonds Farsons Cisk Plc</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>Simonds Farsons Cisk Plc</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>9587</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E162" s="2" t="inlineStr">
+        <is>
+          <t>Mriehel</t>
+        </is>
+      </c>
+      <c r="F162" s="2" t="inlineStr">
+        <is>
+          <t>Mriehel</t>
+        </is>
+      </c>
+      <c r="G162" s="2" t="inlineStr">
+        <is>
+          <t>The Brewery, Mdina Road</t>
+        </is>
+      </c>
+      <c r="H162" s="2" t="inlineStr">
+        <is>
+          <t>CBD 2010</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.farsons.com</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr"/>
+      <c r="K162" s="2" t="inlineStr"/>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>802</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr"/>
+      <c r="N162" s="2" t="inlineStr">
+        <is>
+          <t>careers@farsons.com</t>
+        </is>
+      </c>
+      <c r="O162" s="2" t="inlineStr">
+        <is>
+          <t>+356 2381 4114</t>
+        </is>
+      </c>
+      <c r="P162" s="2" t="inlineStr">
+        <is>
+          <t>1920</t>
+        </is>
+      </c>
+      <c r="Q162" s="2" t="inlineStr">
+        <is>
+          <t>C 113</t>
+        </is>
+      </c>
+      <c r="R162" s="2" t="inlineStr"/>
+      <c r="S162" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/farsonsgroup/</t>
+        </is>
+      </c>
+      <c r="T162" s="2" t="inlineStr"/>
+      <c r="U162" s="2" t="inlineStr"/>
+      <c r="V162" s="2" t="inlineStr"/>
+      <c r="W162" s="2" t="inlineStr"/>
+      <c r="X162" s="2" t="inlineStr"/>
+      <c r="Y162" s="2" t="inlineStr"/>
+      <c r="Z162" s="2" t="inlineStr"/>
+      <c r="AA162" s="2" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>Farsons Beverage Imports Company Limited</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>Farsons Beverage Imports Company Limited</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>9593</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E163" s="2" t="inlineStr">
+        <is>
+          <t>Mdina</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Mdina</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>The Brewery, Mdina Road, Zone 2, Central Business District</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>cbd2010</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>https://farsonsdirect.com</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="inlineStr"/>
+      <c r="K163" s="2" t="inlineStr"/>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr"/>
+      <c r="N163" s="2" t="inlineStr">
+        <is>
+          <t>info@farsonsdirect.com</t>
+        </is>
+      </c>
+      <c r="O163" s="2" t="inlineStr">
+        <is>
+          <t>+356 2381 4444</t>
+        </is>
+      </c>
+      <c r="P163" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="Q163" s="2" t="inlineStr">
+        <is>
+          <t>C 476</t>
+        </is>
+      </c>
+      <c r="R163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/farsonsdirect/</t>
+        </is>
+      </c>
+      <c r="S163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/farsonsdirect/</t>
+        </is>
+      </c>
+      <c r="T163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/farsonsdirect/</t>
+        </is>
+      </c>
+      <c r="U163" s="2" t="inlineStr"/>
+      <c r="V163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@farsonsdirect1770</t>
+        </is>
+      </c>
+      <c r="W163" s="2" t="inlineStr">
+        <is>
+          <t>Petar Mladenovic</t>
+        </is>
+      </c>
+      <c r="X163" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y163" s="2" t="inlineStr"/>
+      <c r="Z163" s="2" t="inlineStr"/>
+      <c r="AA163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/petar-mladenovic-1a9745145/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>THE NUANCE GROUP (Malta) Limited</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Dufry Malta</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>103888</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>Luqa</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Luqa</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>Administration Building, 2nd Floor.</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>LQA 4000</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>https://malta.shopdutyfree.com</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="inlineStr"/>
+      <c r="K164" s="2" t="inlineStr"/>
+      <c r="L164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr"/>
+      <c r="N164" s="2" t="inlineStr">
+        <is>
+          <t>Tngmt@thenuancegroup.com</t>
+        </is>
+      </c>
+      <c r="O164" s="2" t="inlineStr">
+        <is>
+          <t>+356 2326 7100</t>
+        </is>
+      </c>
+      <c r="P164" s="2" t="inlineStr"/>
+      <c r="Q164" s="2" t="inlineStr"/>
+      <c r="R164" s="2" t="inlineStr"/>
+      <c r="S164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/MaltaDutyFree/</t>
+        </is>
+      </c>
+      <c r="T164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/maltadutyfree/</t>
+        </is>
+      </c>
+      <c r="U164" s="2" t="inlineStr"/>
+      <c r="V164" s="2" t="inlineStr"/>
+      <c r="W164" s="2" t="inlineStr"/>
+      <c r="X164" s="2" t="inlineStr"/>
+      <c r="Y164" s="2" t="inlineStr"/>
+      <c r="Z164" s="2" t="inlineStr"/>
+      <c r="AA164" s="2" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Sa Sales Ltd</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Sa Sales Ltd</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>9584</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>Triq l-Intornjatur, Mriehel</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>BKR 3000</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>http://sasalesltd.com</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="inlineStr"/>
+      <c r="K165" s="2" t="inlineStr"/>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr"/>
+      <c r="N165" s="2" t="inlineStr">
+        <is>
+          <t>info@sasalesltd.com</t>
+        </is>
+      </c>
+      <c r="O165" s="2" t="inlineStr">
+        <is>
+          <t>+356 2147 2449</t>
+        </is>
+      </c>
+      <c r="P165" s="2" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="Q165" s="2" t="inlineStr">
+        <is>
+          <t>C 55182</t>
+        </is>
+      </c>
+      <c r="R165" s="2" t="inlineStr"/>
+      <c r="S165" s="2" t="inlineStr"/>
+      <c r="T165" s="2" t="inlineStr"/>
+      <c r="U165" s="2" t="inlineStr"/>
+      <c r="V165" s="2" t="inlineStr"/>
+      <c r="W165" s="2" t="inlineStr"/>
+      <c r="X165" s="2" t="inlineStr"/>
+      <c r="Y165" s="2" t="inlineStr"/>
+      <c r="Z165" s="2" t="inlineStr"/>
+      <c r="AA165" s="2" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>9581</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="F166" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="G166" s="2" t="inlineStr">
+        <is>
+          <t>239 Tower Road</t>
+        </is>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>SLM 1601</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="inlineStr"/>
+      <c r="K166" s="2" t="inlineStr"/>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr"/>
+      <c r="N166" s="2" t="inlineStr">
+        <is>
+          <t>sales@martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="O166" s="2" t="inlineStr">
+        <is>
+          <t>+356 2097 8604</t>
+        </is>
+      </c>
+      <c r="P166" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q166" s="2" t="inlineStr">
+        <is>
+          <t>C14429</t>
+        </is>
+      </c>
+      <c r="R166" s="2" t="inlineStr"/>
+      <c r="S166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/philippe-martinet-fine-wines-174639482587570/</t>
+        </is>
+      </c>
+      <c r="T166" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/philippe_martinet_fine_wines/?hl=en</t>
+        </is>
+      </c>
+      <c r="U166" s="2" t="inlineStr"/>
+      <c r="V166" s="2" t="inlineStr"/>
+      <c r="W166" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet</t>
+        </is>
+      </c>
+      <c r="X166" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y166" s="2" t="inlineStr"/>
+      <c r="Z166" s="2" t="inlineStr"/>
+      <c r="AA166" s="2" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Philippe Martinet Fine Wines Ltd</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>9581</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E167" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="F167" s="2" t="inlineStr">
+        <is>
+          <t>Sliema</t>
+        </is>
+      </c>
+      <c r="G167" s="2" t="inlineStr">
+        <is>
+          <t>239 Tower Road</t>
+        </is>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>SLM 1601</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="inlineStr"/>
+      <c r="K167" s="2" t="inlineStr"/>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr"/>
+      <c r="N167" s="2" t="inlineStr">
+        <is>
+          <t>sales@martinet-finewines.com</t>
+        </is>
+      </c>
+      <c r="O167" s="2" t="inlineStr">
+        <is>
+          <t>+356 2097 8604</t>
+        </is>
+      </c>
+      <c r="P167" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q167" s="2" t="inlineStr">
+        <is>
+          <t>C14429</t>
+        </is>
+      </c>
+      <c r="R167" s="2" t="inlineStr"/>
+      <c r="S167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/philippe-martinet-fine-wines-174639482587570/</t>
+        </is>
+      </c>
+      <c r="T167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/philippe_martinet_fine_wines/?hl=en</t>
+        </is>
+      </c>
+      <c r="U167" s="2" t="inlineStr"/>
+      <c r="V167" s="2" t="inlineStr"/>
+      <c r="W167" s="2" t="inlineStr">
+        <is>
+          <t>Francesca Persico</t>
+        </is>
+      </c>
+      <c r="X167" s="2" t="inlineStr">
+        <is>
+          <t>Sales Specialist</t>
+        </is>
+      </c>
+      <c r="Y167" s="2" t="inlineStr"/>
+      <c r="Z167" s="2" t="inlineStr"/>
+      <c r="AA167" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/francesca-persico-949621102/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>51840</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E168" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="G168" s="2" t="inlineStr">
+        <is>
+          <t>182 Olaf Gollcher</t>
+        </is>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>BKR 4429</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr"/>
+      <c r="K168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr"/>
+      <c r="N168" s="2" t="inlineStr">
+        <is>
+          <t>sales@gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="O168" s="2" t="inlineStr">
+        <is>
+          <t>+356 2033 0140</t>
+        </is>
+      </c>
+      <c r="P168" s="2" t="inlineStr"/>
+      <c r="Q168" s="2" t="inlineStr"/>
+      <c r="R168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gift-hampers/</t>
+        </is>
+      </c>
+      <c r="S168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GiftHampersIntl</t>
+        </is>
+      </c>
+      <c r="T168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gifthampersintl/</t>
+        </is>
+      </c>
+      <c r="U168" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/gifthampersintl</t>
+        </is>
+      </c>
+      <c r="V168" s="2" t="inlineStr"/>
+      <c r="W168" s="2" t="inlineStr">
+        <is>
+          <t>Sarah Booth</t>
+        </is>
+      </c>
+      <c r="X168" s="2" t="inlineStr">
+        <is>
+          <t>Co-founder</t>
+        </is>
+      </c>
+      <c r="Y168" s="2" t="inlineStr"/>
+      <c r="Z168" s="2" t="inlineStr"/>
+      <c r="AA168" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sarahcarterbooth/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>Gift Hampers Malta</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>51840</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>Birkirkara</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>182 Olaf Gollcher</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>BKR 4429</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr"/>
+      <c r="K169" s="2" t="inlineStr"/>
+      <c r="L169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr"/>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>sales@gifthampersmalta.com</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>+356 2033 0140</t>
+        </is>
+      </c>
+      <c r="P169" s="2" t="inlineStr"/>
+      <c r="Q169" s="2" t="inlineStr"/>
+      <c r="R169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/gift-hampers/</t>
+        </is>
+      </c>
+      <c r="S169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/GiftHampersIntl</t>
+        </is>
+      </c>
+      <c r="T169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/gifthampersintl/</t>
+        </is>
+      </c>
+      <c r="U169" s="2" t="inlineStr">
+        <is>
+          <t>https://x.com/gifthampersintl</t>
+        </is>
+      </c>
+      <c r="V169" s="2" t="inlineStr"/>
+      <c r="W169" s="2" t="inlineStr">
+        <is>
+          <t>Jon Fava</t>
+        </is>
+      </c>
+      <c r="X169" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y169" s="2" t="inlineStr"/>
+      <c r="Z169" s="2" t="inlineStr"/>
+      <c r="AA169" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jonfava/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Cellars Ltd.</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>Patrick Cellars Ltd.</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>9580</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>Birżebbuġa</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>164, Birżebbġa Road</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>BBG1507</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.patrickcellars.com</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr"/>
+      <c r="K170" s="2" t="inlineStr"/>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr"/>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>info@patrickcellars.com</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>+356 2165 0810</t>
+        </is>
+      </c>
+      <c r="P170" s="2" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="Q170" s="2" t="inlineStr">
+        <is>
+          <t>C 15930</t>
+        </is>
+      </c>
+      <c r="R170" s="2" t="inlineStr"/>
+      <c r="S170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/PatrickCellarsltd</t>
+        </is>
+      </c>
+      <c r="T170" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/patrick_cellars_ltd/</t>
+        </is>
+      </c>
+      <c r="U170" s="2" t="inlineStr"/>
+      <c r="V170" s="2" t="inlineStr"/>
+      <c r="W170" s="2" t="inlineStr"/>
+      <c r="X170" s="2" t="inlineStr"/>
+      <c r="Y170" s="2" t="inlineStr"/>
+      <c r="Z170" s="2" t="inlineStr"/>
+      <c r="AA170" s="2" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>9570</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>Triq San Anton Abbati</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>MST 3102</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dicalhouse.com</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr"/>
+      <c r="K171" s="2" t="inlineStr"/>
+      <c r="L171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr"/>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>foods@dicalgroup.com</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>+356 2142 4601</t>
+        </is>
+      </c>
+      <c r="P171" s="2" t="inlineStr"/>
+      <c r="Q171" s="2" t="inlineStr"/>
+      <c r="R171" s="2" t="inlineStr"/>
+      <c r="S171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DicalHouseMosta/</t>
+        </is>
+      </c>
+      <c r="T171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dicalhouse/</t>
+        </is>
+      </c>
+      <c r="U171" s="2" t="inlineStr"/>
+      <c r="V171" s="2" t="inlineStr"/>
+      <c r="W171" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Calleja</t>
+        </is>
+      </c>
+      <c r="X171" s="2" t="inlineStr">
+        <is>
+          <t>Director</t>
+        </is>
+      </c>
+      <c r="Y171" s="2" t="inlineStr"/>
+      <c r="Z171" s="2" t="inlineStr"/>
+      <c r="AA171" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dominic-calleja-57335024/?originalSubdomain=mt</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>Dical House</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>9570</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>Il-Mosta</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>Triq San Anton Abbati</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>MST 3102</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.dicalhouse.com</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr"/>
+      <c r="K172" s="2" t="inlineStr"/>
+      <c r="L172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr"/>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>foods@dicalgroup.com</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>+356 2142 4601</t>
+        </is>
+      </c>
+      <c r="P172" s="2" t="inlineStr"/>
+      <c r="Q172" s="2" t="inlineStr"/>
+      <c r="R172" s="2" t="inlineStr"/>
+      <c r="S172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/DicalHouseMosta/</t>
+        </is>
+      </c>
+      <c r="T172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dicalhouse/</t>
+        </is>
+      </c>
+      <c r="U172" s="2" t="inlineStr"/>
+      <c r="V172" s="2" t="inlineStr"/>
+      <c r="W172" s="2" t="inlineStr">
+        <is>
+          <t>Anamaria Stivala</t>
+        </is>
+      </c>
+      <c r="X172" s="2" t="inlineStr">
+        <is>
+          <t>Manager And Owner</t>
+        </is>
+      </c>
+      <c r="Y172" s="2" t="inlineStr"/>
+      <c r="Z172" s="2" t="inlineStr"/>
+      <c r="AA172" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/anamaria-stivala-22b26569/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
